--- a/links/Juegos_PSVITA.xlsx
+++ b/links/Juegos_PSVITA.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:Q18"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
     <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
     <col min="7" max="7" width="35.83203125" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
@@ -416,11 +416,6 @@
     <col min="15" max="15" width="35.83203125" customWidth="1"/>
     <col min="16" max="16" width="35.83203125" customWidth="1"/>
     <col min="17" max="17" width="35.83203125" customWidth="1"/>
-    <col min="18" max="18" width="35.83203125" customWidth="1"/>
-    <col min="19" max="19" width="35.83203125" customWidth="1"/>
-    <col min="20" max="20" width="35.83203125" customWidth="1"/>
-    <col min="21" max="21" width="35.83203125" customWidth="1"/>
-    <col min="22" max="22" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -437,57 +432,42 @@
         <v>Imagen Local</v>
       </c>
       <c r="E1" t="str">
+        <v>Sinopsis</v>
+      </c>
+      <c r="F1" t="str">
         <v>En Varias Partes</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Mega</v>
       </c>
-      <c r="G1" t="str">
-        <v>Mega Parte 1</v>
-      </c>
       <c r="H1" t="str">
-        <v>Mega Parte 2</v>
+        <v>Mediafire</v>
       </c>
       <c r="I1" t="str">
-        <v>Mediafire</v>
+        <v>1Fichier</v>
       </c>
       <c r="J1" t="str">
-        <v>Mediafire Parte 1</v>
+        <v>Google Drive</v>
       </c>
       <c r="K1" t="str">
-        <v>Mediafire Parte 2</v>
+        <v>Qiwi</v>
       </c>
       <c r="L1" t="str">
-        <v>1Fichier</v>
+        <v>Pixeldrain</v>
       </c>
       <c r="M1" t="str">
-        <v>Google Drive</v>
+        <v>Megaup</v>
       </c>
       <c r="N1" t="str">
-        <v>Google Drive Parte 1</v>
+        <v>Otro Link 1</v>
       </c>
       <c r="O1" t="str">
-        <v>Google Drive Parte 2</v>
+        <v>Otro Link 2</v>
       </c>
       <c r="P1" t="str">
-        <v>Qiwi</v>
+        <v>Otro Link 3</v>
       </c>
       <c r="Q1" t="str">
-        <v>Pixeldrain</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Megaup</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Otro Link 1</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Otro Link 2</v>
-      </c>
-      <c r="U1" t="str">
-        <v>Otro Link 3</v>
-      </c>
-      <c r="V1" t="str">
         <v>Otro Link 4</v>
       </c>
     </row>
@@ -505,24 +485,21 @@
         <v>imagenes/PSVITA/FIFA 19 Mod Final.jpg</v>
       </c>
       <c r="E2" t="str">
-        <v>No</v>
-      </c>
-      <c r="G2" t="str">
-        <v>https://mega.nz/#!ayQUAKJB!5gY8Y-OgnkSMIbwf3v4qkxb7iC2q1pXkMRhUnVLyerw</v>
-      </c>
-      <c r="H2" t="str">
-        <v>https://mega.nz/#!T2IWzKTA!c2kOuKk54P5uhE3J0TtF3NIAO2NhjjS7wxjRTWY2rX0</v>
-      </c>
-      <c r="S2" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T2" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U2" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V2" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F2" t="str">
+        <v>No</v>
+      </c>
+      <c r="N2" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O2" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P2" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q2" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -540,24 +517,27 @@
         <v>imagenes/PSVITA/Devious Dungeon.jpg</v>
       </c>
       <c r="E3" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F3" t="str">
+        <v>No</v>
+      </c>
+      <c r="G3" t="str">
         <v>https://mega.nz/#!vOhimIbS!1lpNPeE6vGR9Nd8ZndXm-KcogNqFrW0Ko5j80ieqQTk</v>
       </c>
-      <c r="I3" t="str">
+      <c r="H3" t="str">
         <v>http://www.mediafire.com/file/ytjqx8v7qmro3ll/%5BGM%5DDD%5BUS%5D.zip</v>
       </c>
-      <c r="S3" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T3" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U3" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V3" t="str">
+      <c r="N3" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O3" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P3" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q3" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -575,27 +555,30 @@
         <v>imagenes/PSVITA/Hakuoki Edo Blossoms.jpg</v>
       </c>
       <c r="E4" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F4" t="str">
+        <v>No</v>
+      </c>
+      <c r="G4" t="str">
         <v>https://mega.nz/#!HnZQSCLC!zcCFrTyPkX1-p_842JZxlcqJo1xVYQI11M92-RuLgkg</v>
       </c>
-      <c r="I4" t="str">
+      <c r="H4" t="str">
         <v>http://www.mediafire.com/file/6jdipluxa3wk0ep/%5BGM%5DHEB%5BEU%5D.zip</v>
       </c>
-      <c r="M4" t="str">
+      <c r="J4" t="str">
         <v>https://drive.google.com/uc?id=1u4OvbhAqpj4pzoBry-9di313NwE-7uDz&amp;export=download</v>
       </c>
-      <c r="S4" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T4" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U4" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V4" t="str">
+      <c r="N4" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O4" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P4" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q4" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -613,27 +596,30 @@
         <v>imagenes/PSVITA/Bullet Girls Phantasia.jpg</v>
       </c>
       <c r="E5" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F5" t="str">
+        <v>No</v>
+      </c>
+      <c r="G5" t="str">
         <v>https://mega.nz/#!HrxFDQZb!-tkiW5rtW9BT0keZlqCLKzmTJfkpDvgTlAYe1MIDxw4</v>
       </c>
-      <c r="I5" t="str">
+      <c r="H5" t="str">
         <v>http://www.mediafire.com/file/sdvc50dr6ec9duk/%5BGM%5DBGP%2B25xDLC%5BAS%5D.zip</v>
       </c>
-      <c r="M5" t="str">
+      <c r="J5" t="str">
         <v>https://drive.google.com/uc?id=1CLMZ62zHpF76TdtqJkiKG1dCZwHu9BDi&amp;export=download</v>
       </c>
-      <c r="S5" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T5" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U5" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V5" t="str">
+      <c r="N5" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O5" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P5" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q5" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -651,24 +637,27 @@
         <v>imagenes/PSVITA/Punch Line.jpg</v>
       </c>
       <c r="E6" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F6" t="str">
+        <v>No</v>
+      </c>
+      <c r="G6" t="str">
         <v>https://filecrypt.cc/Container/1F206CF0F6.html</v>
       </c>
-      <c r="M6" t="str">
+      <c r="J6" t="str">
         <v>https://drive.google.com/file/d/16ZYsmGuop5mvGK5POfcYitXq4DhvQAI_/view</v>
       </c>
-      <c r="S6" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T6" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U6" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V6" t="str">
+      <c r="N6" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O6" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P6" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q6" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -686,21 +675,24 @@
         <v>imagenes/PSVITA/The Long Reach.jpg</v>
       </c>
       <c r="E7" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F7" t="str">
+        <v>No</v>
+      </c>
+      <c r="G7" t="str">
         <v>https://filecrypt.cc/Container/0E706CF21C.html</v>
       </c>
-      <c r="S7" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T7" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U7" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V7" t="str">
+      <c r="N7" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O7" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P7" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q7" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -718,27 +710,30 @@
         <v>imagenes/PSVITA/Fernz Gate.jpg</v>
       </c>
       <c r="E8" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F8" t="str">
+        <v>No</v>
+      </c>
+      <c r="G8" t="str">
         <v>https://mega.nz/#!v2hChSzI!deO8kUmAw7pqz1BKlICSK497XxLDIu0wy2pDBTniPN0</v>
       </c>
-      <c r="I8" t="str">
+      <c r="H8" t="str">
         <v>http://www.mediafire.com/file/x8n8cmmulb6tzzi/%5BGM%5DFGT%5BUS%5D.zip</v>
       </c>
-      <c r="M8" t="str">
+      <c r="J8" t="str">
         <v>https://drive.google.com/uc?id=1lDZqNs524eaSspwaeFVHxSpreB2MLQDD&amp;export=download</v>
       </c>
-      <c r="S8" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T8" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U8" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V8" t="str">
+      <c r="N8" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O8" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P8" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q8" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -756,27 +751,30 @@
         <v>imagenes/PSVITA/Gem Smashers.jpg</v>
       </c>
       <c r="E9" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F9" t="str">
+        <v>No</v>
+      </c>
+      <c r="G9" t="str">
         <v>https://mega.nz/#!nyR3wSyJ!zksWbw_WgXdoVW9alOeKKuTbsXulhyG-83f2bCTKxYk</v>
       </c>
-      <c r="I9" t="str">
+      <c r="H9" t="str">
         <v>http://www.mediafire.com/file/9k9nd14x2tbdtxw/%5BGM%5DGMSM%5BEU%5D.zip</v>
       </c>
-      <c r="M9" t="str">
+      <c r="J9" t="str">
         <v>https://drive.google.com/uc?id=1x92KnHiUxFKOa2SxVLubvv4MW9ZD51Sx&amp;export=download</v>
       </c>
-      <c r="S9" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T9" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U9" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V9" t="str">
+      <c r="N9" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O9" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P9" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q9" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -794,36 +792,21 @@
         <v>imagenes/PSVITA/TETRAs Escape.jpg</v>
       </c>
       <c r="E10" t="str">
-        <v>No</v>
-      </c>
-      <c r="G10" t="str">
-        <v>https://mega.nz/#!OnZFQCjI!7NMzdq9oN6Jgqjzp4GTxZrCf_Cwt5ovbei2xnjoAQBo</v>
-      </c>
-      <c r="H10" t="str">
-        <v>https://mega.nz/#!GmADyS5S!FjhtPfmWxQZzgKmn5haXg64lEEJzmpZORppIgM_uUaU</v>
-      </c>
-      <c r="J10" t="str">
-        <v>http://www.mediafire.com/file/67raxj7372zar91/%5BGM%5DTESC%5BUS%5D.zip</v>
-      </c>
-      <c r="K10" t="str">
-        <v>http://www.mediafire.com/file/t9qh8q8uo97l6zu/%5BGM%5DTESC%5BEU%5D.zip</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F10" t="str">
+        <v>No</v>
       </c>
       <c r="N10" t="str">
-        <v>https://drive.google.com/uc?id=1K9CCdiTlDa7LekRkc8uGg5xqbjKVugpV&amp;export=download</v>
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
       </c>
       <c r="O10" t="str">
-        <v>https://drive.google.com/uc?id=19z_qnw9XoJ0uT_gCxZa0cJElLwjDQ2SP&amp;export=download</v>
-      </c>
-      <c r="S10" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T10" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U10" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V10" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P10" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q10" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -841,36 +824,21 @@
         <v>imagenes/PSVITA/Super Skull Smash GO 2 Turbo.jpg</v>
       </c>
       <c r="E11" t="str">
-        <v>No</v>
-      </c>
-      <c r="G11" t="str">
-        <v>https://mega.nz/#!Xu5GUQKC!qHfY7Z3gMoMCu4r8ddo1idA9vloPOZlk8NXCuXVjrOE</v>
-      </c>
-      <c r="H11" t="str">
-        <v>https://mega.nz/#!z6oQzA6D!89kGe9fhmP9kdC1ba4Me-vRPnQKt5_qww-672vvNEDQ</v>
-      </c>
-      <c r="J11" t="str">
-        <v>http://www.mediafire.com/file/p1cqi86f16mv46f/%5BGM%5DSKSG2T%5BUS%5D.zip</v>
-      </c>
-      <c r="K11" t="str">
-        <v>http://www.mediafire.com/file/hnm1v1k2tga4yym/%5BGM%5DSKSG2T%5BEU%5D.zip</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F11" t="str">
+        <v>No</v>
       </c>
       <c r="N11" t="str">
-        <v>https://drive.google.com/uc?authuser=0&amp;id=13IyrvTmvo-AHBBOwWg-kFYoRoWNKhmW0&amp;export=download</v>
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
       </c>
       <c r="O11" t="str">
-        <v>https://drive.google.com/uc?authuser=0&amp;id=1cbNjI5bDURVQoZTcFM5oSlBxOrIDAEFN&amp;export=download</v>
-      </c>
-      <c r="S11" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T11" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U11" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V11" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P11" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q11" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -888,27 +856,30 @@
         <v>imagenes/PSVITA/Super Robot Wars X.jpg</v>
       </c>
       <c r="E12" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F12" t="str">
+        <v>No</v>
+      </c>
+      <c r="G12" t="str">
         <v>https://mega.nz/#!T3RijQQY!ADi42_6nw1yyazGSSzTWDdX7UMdKWGUvH4Cqfd5i-Q4</v>
       </c>
-      <c r="I12" t="str">
+      <c r="H12" t="str">
         <v>http://www.mediafire.com/file/vx7goon3nc8x16o/%5BGM%5DSRWX3xDLC%5BASIA%5D.rar/file</v>
       </c>
-      <c r="M12" t="str">
+      <c r="J12" t="str">
         <v>https://drive.google.com/uc?id=1U-PFMTglI3dWr6VyVT5FDEBmTEsOYgn3&amp;export=download</v>
       </c>
-      <c r="S12" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T12" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U12" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V12" t="str">
+      <c r="N12" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O12" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P12" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q12" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -926,27 +897,30 @@
         <v>imagenes/PSVITA/FullBlast.jpg</v>
       </c>
       <c r="E13" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F13" t="str">
+        <v>No</v>
+      </c>
+      <c r="G13" t="str">
         <v>https://mega.nz/#!DOxniQhI!-me7IwM5hpk8ZTqvUSqbqQcB4nelLIX-lWtx3PnckkY</v>
       </c>
-      <c r="I13" t="str">
+      <c r="H13" t="str">
         <v>http://www.mediafire.com/file/ya9deameblccmcc/%5BGM%5DFLLBLST%5BUS%5D.zip</v>
       </c>
-      <c r="M13" t="str">
+      <c r="J13" t="str">
         <v>https://drive.google.com/uc?id=1tULp2k-P8p2YONcTZlHK7skG7TvUbKaZ&amp;export=download</v>
       </c>
-      <c r="S13" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T13" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U13" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V13" t="str">
+      <c r="N13" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O13" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P13" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q13" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -964,24 +938,27 @@
         <v>imagenes/PSVITA/KOI.jpg</v>
       </c>
       <c r="E14" t="str">
-        <v>No</v>
-      </c>
-      <c r="I14" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F14" t="str">
+        <v>No</v>
+      </c>
+      <c r="H14" t="str">
         <v>http://www.mediafire.com/file/3oocm7f380r7q0i/%5BGM%5DK0I%5BUS%5D.zip</v>
       </c>
-      <c r="M14" t="str">
+      <c r="J14" t="str">
         <v>https://drive.google.com/uc?id=1oMZiDYyOtyYCYg-ePuuB13wWbbISXvjQ&amp;export=download</v>
       </c>
-      <c r="S14" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T14" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U14" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V14" t="str">
+      <c r="N14" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O14" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P14" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q14" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -999,27 +976,30 @@
         <v>imagenes/PSVITA/Pato Box.jpg</v>
       </c>
       <c r="E15" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F15" t="str">
+        <v>No</v>
+      </c>
+      <c r="G15" t="str">
         <v>https://mega.nz/#!77BSSIiJ!o5NknDsJQC76dQAoXGFGehl_OjY96C1ZLwX5ETjqhXs</v>
       </c>
-      <c r="I15" t="str">
+      <c r="H15" t="str">
         <v>https://www.mediafire.com/file/zmcddjz4w3jhmgk/%5BGM%5DPTBX%5BUS%5D.zip</v>
       </c>
-      <c r="M15" t="str">
+      <c r="J15" t="str">
         <v>https://drive.google.com/uc?id=1rstQCTQC8xgZzLuJP4j3Te19ULnj5LOB&amp;export=download</v>
       </c>
-      <c r="S15" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T15" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U15" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V15" t="str">
+      <c r="N15" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O15" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P15" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q15" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1037,27 +1017,30 @@
         <v>imagenes/PSVITA/Timespinner.jpg</v>
       </c>
       <c r="E16" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F16" t="str">
+        <v>No</v>
+      </c>
+      <c r="G16" t="str">
         <v>https://mega.nz/#!b3RwkAYQ!o-JnD604DivuFnJCuV7KSFaw_A4sQPup_X_8pDffaqk</v>
       </c>
-      <c r="I16" t="str">
+      <c r="H16" t="str">
         <v>https://www.mediafire.com/file/080vbaj3bd20e93/%5BGM%5DTMSPNNRv101%5BUS%5D.zip</v>
       </c>
-      <c r="M16" t="str">
+      <c r="J16" t="str">
         <v>https://drive.google.com/uc?id=1Jh7gPmvuhKC4cNR-9TqjmNegWjGejWax&amp;export=download</v>
       </c>
-      <c r="S16" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T16" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U16" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V16" t="str">
+      <c r="N16" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O16" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P16" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q16" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1075,24 +1058,27 @@
         <v>imagenes/PSVITA/Licky The Lucky Lizard Lives.jpg</v>
       </c>
       <c r="E17" t="str">
-        <v>No</v>
-      </c>
-      <c r="I17" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F17" t="str">
+        <v>No</v>
+      </c>
+      <c r="H17" t="str">
         <v>https://www.mediafire.com/file/kbqwfr82l4f1bnf/%5BGM%5DLTLLLA%5BUS%5D.zip</v>
       </c>
-      <c r="M17" t="str">
+      <c r="J17" t="str">
         <v>https://drive.google.com/uc?authuser=0&amp;id=1eLNP_kJ0ZOpGgRHz52yQ7t6XACuAGvgZ&amp;export=download</v>
       </c>
-      <c r="S17" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T17" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U17" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V17" t="str">
+      <c r="N17" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O17" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P17" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q17" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1110,33 +1096,36 @@
         <v>imagenes/PSVITA/Fast Striker.jpg</v>
       </c>
       <c r="E18" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F18" t="str">
+        <v>No</v>
+      </c>
+      <c r="G18" t="str">
         <v>https://mega.nz/#!ohlETSqa!IH5jZI-Q6kUH5tgdV5nl0JmhoC2-z3aXnnsuVTvDj4o</v>
       </c>
-      <c r="I18" t="str">
+      <c r="H18" t="str">
         <v>https://www.mediafire.com/file/sgbh6hbb275muxf/%5BGM%5DFSTS%5BUS%5D.zip</v>
       </c>
-      <c r="M18" t="str">
+      <c r="J18" t="str">
         <v>https://drive.google.com/uc?authuser=0&amp;id=1YoyrbR47xvPyajpjW8yL4zhxvoih9yjW&amp;export=download</v>
       </c>
-      <c r="S18" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
-      </c>
-      <c r="T18" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
-      </c>
-      <c r="U18" t="str">
-        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
-      </c>
-      <c r="V18" t="str">
+      <c r="N18" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-nonpdrm-plugin-psvita/</v>
+      </c>
+      <c r="O18" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-install-maidumptool-psvita/</v>
+      </c>
+      <c r="P18" t="str">
+        <v>https://downloadgamepsp.org/guide/how-to-installing-dlc-updates-maidumptool-psvita/</v>
+      </c>
+      <c r="Q18" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q18"/>
   </ignoredErrors>
 </worksheet>
 </file>